--- a/travel/IT_travel_photodata.xlsx
+++ b/travel/IT_travel_photodata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01.RLFdata\09.RLF_Software\5.RLF_Websites\3.GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{20B37F2F-8137-4B9A-8CDE-0BF913DD7EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621ABA9E-63B3-4D46-9ECA-4E953AFD153C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33480" yWindow="2400" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -417,9 +417,6 @@
     <t>Neuschwanstein Castle</t>
   </si>
   <si>
-    <t>NeuschwansteinCastle.GE.jpg</t>
-  </si>
-  <si>
     <t>Statue of Liberty, New York</t>
   </si>
   <si>
@@ -546,45 +543,24 @@
     <t>Morón de la Frontera</t>
   </si>
   <si>
-    <t>Moron.Spain.jpg</t>
-  </si>
-  <si>
     <t>Mall of America / Nickelodeon Universe, Bloomington</t>
   </si>
   <si>
-    <t>MallAmericas.Bloomington.MN.jpg</t>
-  </si>
-  <si>
     <t>Clear Lake / Houston area (approx.)</t>
   </si>
   <si>
-    <t>RLFmentorFredHaiseApollo13.ClearLake.TX.jpg</t>
-  </si>
-  <si>
     <t>Smithsonian National Air and Space Museum, Washington DC</t>
   </si>
   <si>
-    <t>AirSpaceSmithsonian.WDC.jpg</t>
-  </si>
-  <si>
     <t>State Fair of Texas, Fair Park, Dallas</t>
   </si>
   <si>
-    <t>TxStateFair.Dallas.TX.jpg</t>
-  </si>
-  <si>
     <t>Big Bend National Park – Chisos Basin area (approx.)</t>
   </si>
   <si>
-    <t>BigBendNP.TX.jpg</t>
-  </si>
-  <si>
     <t>Camino de Santiago mural, Logroño</t>
   </si>
   <si>
-    <t>Camino.Logrono.LaRioja.Spain.jpg</t>
-  </si>
-  <si>
     <t>RunningBulls.Pamplona.Spain.JPG</t>
   </si>
   <si>
@@ -702,9 +678,6 @@
     <t>Gorges de Cauterets – Tour de France route (approx.)</t>
   </si>
   <si>
-    <t>GorgesDeCauterets.TourDeFrance.France.jpg</t>
-  </si>
-  <si>
     <t>Checkpoint Charlie, Berlin</t>
   </si>
   <si>
@@ -726,9 +699,6 @@
     <t>Alcázar of Segovia</t>
   </si>
   <si>
-    <t>alcazar.segovia.spain.jpg</t>
-  </si>
-  <si>
     <t>Park Güell, Barcelona</t>
   </si>
   <si>
@@ -829,6 +799,36 @@
   </si>
   <si>
     <t>Cancun / Cozumel</t>
+  </si>
+  <si>
+    <t>GorgesDeCauterets.TourDeFrance.France.JPG</t>
+  </si>
+  <si>
+    <t>NeuschwansteinCastle.GE.JPG</t>
+  </si>
+  <si>
+    <t>alcazar.segovia.spain.JPG</t>
+  </si>
+  <si>
+    <t>Camino.Logrono.LaRioja.Spain.JPG</t>
+  </si>
+  <si>
+    <t>Moron.Spain.JPG</t>
+  </si>
+  <si>
+    <t>AirSpaceSmithsonian.WDC.JPG</t>
+  </si>
+  <si>
+    <t>BigBendNP.TX.JPG</t>
+  </si>
+  <si>
+    <t>MallAmericas.Bloomington.MN.JPG</t>
+  </si>
+  <si>
+    <t>RLFmentorFredHaiseApollo13.ClearLake.TX.JPG</t>
+  </si>
+  <si>
+    <t>TxStateFair.Dallas.TX.JPG</t>
   </si>
 </sst>
 </file>
@@ -1203,19 +1203,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1447,10 +1447,10 @@
         <v>151.21549999999999</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>26</v>
@@ -1484,10 +1484,10 @@
         <v>79</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1501,10 +1501,10 @@
         <v>79</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1518,10 +1518,10 @@
         <v>60</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1552,10 +1552,10 @@
         <v>60</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1566,10 +1566,10 @@
         <v>116.39749999999999</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>27</v>
@@ -1583,7 +1583,7 @@
         <v>116.57040000000001</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>45</v>
@@ -1600,10 +1600,10 @@
         <v>109.27849999999999</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>28</v>
@@ -1617,13 +1617,13 @@
         <v>14.4213</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1691,7 +1691,7 @@
         <v>98</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1736,13 +1736,13 @@
         <v>24.742799999999999</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="E32" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1790,10 +1790,10 @@
         <v>76</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>221</v>
+        <v>254</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1824,10 +1824,10 @@
         <v>76</v>
       </c>
       <c r="D37" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1841,10 +1841,10 @@
         <v>76</v>
       </c>
       <c r="D38" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1858,10 +1858,10 @@
         <v>76</v>
       </c>
       <c r="D39" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1875,10 +1875,10 @@
         <v>73</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1946,7 +1946,7 @@
         <v>125</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>126</v>
+        <v>255</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1960,10 +1960,10 @@
         <v>73</v>
       </c>
       <c r="D45" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1977,10 +1977,10 @@
         <v>73</v>
       </c>
       <c r="D46" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2059,10 +2059,10 @@
         <v>8.9339999999999993</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>37</v>
@@ -2076,13 +2076,13 @@
         <v>12.339700000000001</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="E52" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2093,10 +2093,10 @@
         <v>9.1896000000000004</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>38</v>
@@ -2110,7 +2110,7 @@
         <v>10.3948</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>31</v>
@@ -2127,7 +2127,7 @@
         <v>14.4841</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>32</v>
@@ -2144,10 +2144,10 @@
         <v>12.4915</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>30</v>
@@ -2161,10 +2161,10 @@
         <v>129.86320000000001</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>53</v>
@@ -2198,10 +2198,10 @@
         <v>111</v>
       </c>
       <c r="D59" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E59" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2212,10 +2212,10 @@
         <v>-86.990799999999993</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>48</v>
@@ -2246,10 +2246,10 @@
         <v>-3.9847999999999999</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>58</v>
@@ -2263,7 +2263,7 @@
         <v>-5.8102</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>43</v>
@@ -2314,13 +2314,13 @@
         <v>-25.675599999999999</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2337,7 +2337,7 @@
         <v>67</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2368,10 +2368,10 @@
         <v>66</v>
       </c>
       <c r="D69" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2382,10 +2382,10 @@
         <v>-6.3615000000000004</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>47</v>
@@ -2399,10 +2399,10 @@
         <v>-8.5452999999999992</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>54</v>
@@ -2416,10 +2416,10 @@
         <v>-5.9878</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>55</v>
@@ -2433,13 +2433,13 @@
         <v>-4.1326999999999998</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2450,13 +2450,13 @@
         <v>2.1526999999999998</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2467,13 +2467,13 @@
         <v>-2.4449999999999998</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>181</v>
+        <v>257</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2484,13 +2484,13 @@
         <v>-5.4546000000000001</v>
       </c>
       <c r="C76" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="E76" s="3" t="s">
-        <v>169</v>
+        <v>258</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2501,13 +2501,13 @@
         <v>-1.6425000000000001</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2518,13 +2518,13 @@
         <v>18.071100000000001</v>
       </c>
       <c r="C78" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="E78" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2569,13 +2569,13 @@
         <v>28.976800000000001</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2606,7 +2606,7 @@
         <v>88</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>52</v>
@@ -2623,7 +2623,7 @@
         <v>88</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>57</v>
@@ -2640,7 +2640,7 @@
         <v>88</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>46</v>
@@ -2657,7 +2657,7 @@
         <v>88</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>40</v>
@@ -2674,10 +2674,10 @@
         <v>88</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>175</v>
+        <v>259</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2691,10 +2691,10 @@
         <v>88</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2725,10 +2725,10 @@
         <v>88</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>171</v>
+        <v>261</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2742,10 +2742,10 @@
         <v>88</v>
       </c>
       <c r="D91" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E91" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2759,10 +2759,10 @@
         <v>88</v>
       </c>
       <c r="D92" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E92" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2776,10 +2776,10 @@
         <v>88</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>173</v>
+        <v>262</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2793,10 +2793,10 @@
         <v>88</v>
       </c>
       <c r="D94" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E94" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2810,10 +2810,10 @@
         <v>88</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2827,10 +2827,10 @@
         <v>88</v>
       </c>
       <c r="D96" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2844,10 +2844,10 @@
         <v>88</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>177</v>
+        <v>263</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2872,152 +2872,152 @@
   <sheetData>
     <row r="4" spans="1:1" ht="15.5">
       <c r="A4" s="1" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.5">
       <c r="A5" s="1" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.5">
       <c r="A6" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15.5">
       <c r="A7" s="1" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.5">
       <c r="A8" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15.5">
       <c r="A9" s="1" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.5">
       <c r="A10" s="1" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="15.5">
       <c r="A11" s="1" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.5">
       <c r="A12" s="1" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="15.5">
       <c r="A13" s="1" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15.5">
       <c r="A14" s="1" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15.5">
       <c r="A15" s="1" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="15.5">
       <c r="A16" s="1" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.5">
       <c r="A17" s="1" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.5">
       <c r="A18" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15.5">
       <c r="A19" s="1" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15.5">
       <c r="A20" s="1" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15.5">
       <c r="A21" s="1" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15.5">
       <c r="A22" s="1" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15.5">
       <c r="A23" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="15.5">
       <c r="A24" s="1" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="15.5">
       <c r="A25" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="15.5">
       <c r="A26" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="15.5">
       <c r="A27" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="15.5">
       <c r="A28" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="15.5">
       <c r="A29" s="1" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="15.5">
       <c r="A30" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="15.5">
       <c r="A31" s="1" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="15.5">
       <c r="A32" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="15.5">
       <c r="A33" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="15.5">
@@ -3028,27 +3028,27 @@
     </row>
     <row r="36" spans="1:1" ht="15.5">
       <c r="A36" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="15.5">
       <c r="A37" s="1" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="15.5">
       <c r="A38" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="15.5">
       <c r="A39" s="1" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="15.5">
       <c r="A40" s="1" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="15.5">

--- a/travel/IT_travel_photodata.xlsx
+++ b/travel/IT_travel_photodata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01.RLFdata\09.RLF_Software\5.RLF_Websites\1.IntrepidTexan_development\Website Updates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FEAC697-137D-4A45-90A0-ED697CC7212A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C56487-62D9-4500-A740-1BB241A267D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33480" yWindow="2400" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -939,9 +939,6 @@
     <t>GrandMasterPalace.Rhodes.Greece.JPG</t>
   </si>
   <si>
-    <t>Mandraki Harbour and Fort St. Nicholas, Rhodes</t>
-  </si>
-  <si>
     <t>MandrakiHarbour.Rhodes.Greece.JPG</t>
   </si>
   <si>
@@ -1015,6 +1012,9 @@
   </si>
   <si>
     <t>Areopagus Hill - Apostle Paul brought gospel to Greeks here, Athens</t>
+  </si>
+  <si>
+    <t>Colossus of Rhodes site, Mandraki Harbour, Rhodes</t>
   </si>
 </sst>
 </file>
@@ -1471,7 +1471,7 @@
         <v>111</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -1488,7 +1488,7 @@
         <v>112</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -1536,7 +1536,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>9</v>
@@ -2182,7 +2182,7 @@
         <v>292</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>297</v>
@@ -2199,10 +2199,10 @@
         <v>292</v>
       </c>
       <c r="D48" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="E48" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
@@ -2216,10 +2216,10 @@
         <v>292</v>
       </c>
       <c r="D49" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="E49" s="4" t="s">
         <v>305</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
@@ -2233,10 +2233,10 @@
         <v>292</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
@@ -2250,10 +2250,10 @@
         <v>292</v>
       </c>
       <c r="D51" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
@@ -2284,10 +2284,10 @@
         <v>292</v>
       </c>
       <c r="D53" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>300</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
@@ -2301,10 +2301,10 @@
         <v>292</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
@@ -2658,7 +2658,7 @@
         <v>61</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>126</v>
@@ -3219,10 +3219,10 @@
         <v>203</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
@@ -3236,10 +3236,10 @@
         <v>203</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E109" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
@@ -3270,7 +3270,7 @@
         <v>83</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>8</v>
@@ -3525,10 +3525,10 @@
         <v>83</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
@@ -3627,10 +3627,10 @@
         <v>281</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
